--- a/bin/Debug/net9.0-windows/运行日志/Forms.xlsx
+++ b/bin/Debug/net9.0-windows/运行日志/Forms.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t>OID</t>
   </si>
@@ -59,13 +59,13 @@
     <t>LinkFormOID</t>
   </si>
   <si>
-    <t>HTWT</t>
+    <t>SI</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>身高体重检查</t>
+    <t>Subject Information</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -83,55 +83,625 @@
     <t>NoLink</t>
   </si>
   <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Subject Visits</t>
+  </si>
+  <si>
+    <t>SV2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ICF</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Informed consent</t>
+  </si>
+  <si>
+    <t>Landscape</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>MH_DH</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Disease history and condition</t>
+  </si>
+  <si>
     <t>MH</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>既往病史</t>
-  </si>
-  <si>
-    <t>Landscape</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PC5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Pharmacokinetics sample collection_Q2W_Dose Escalation Part</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Medical History</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Allergic history</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Somking and drinking history</t>
+  </si>
+  <si>
+    <t>TU_TL</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Tumor Results-Baseline Target lesions</t>
+  </si>
+  <si>
+    <t>TU_NTL</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Tumor Results-Baseline Non-Target lesions</t>
+  </si>
+  <si>
+    <t>PR_ANMYN</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Prior Anti-Cancer Therapy-Medication summary</t>
+  </si>
+  <si>
+    <t>PR_ANM</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Prior Anti-Cancer Therapy-medication</t>
+  </si>
+  <si>
+    <t>PR_RAD</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Prior Anti-Cancer Radiation Therapy</t>
+  </si>
+  <si>
+    <t>PR_ANT</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Prior Anti-Cancer Surgery and Procedure</t>
+  </si>
+  <si>
+    <t>VS1</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Vital Signs (Single timepoint)</t>
+  </si>
+  <si>
+    <t>VS2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Vital Signs (Multiple Timepoints)</t>
+  </si>
+  <si>
+    <t>VS_HTWT</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Height and Weight</t>
   </si>
   <si>
     <t>PE</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>体格检查</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Physical Examination</t>
+  </si>
+  <si>
+    <t>ECOG</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>ECOG Performance Status</t>
+  </si>
+  <si>
+    <t>EG1</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>12-Lead Electrocardiogram (single timepoint)</t>
+  </si>
+  <si>
+    <t>EG2</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Triplicate 12-Lead Electrocardiogram</t>
+  </si>
+  <si>
+    <t>EG3</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>12-Lead Electrocardiogram (Multiple timpoint)</t>
+  </si>
+  <si>
+    <t>ECMU</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Echocardiogram/Multigated Acquisition</t>
+  </si>
+  <si>
+    <t>LB2</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Myocardial Enzymes</t>
+  </si>
+  <si>
+    <t>LB_HEM</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Hematology</t>
+  </si>
+  <si>
+    <t>LB_CHEM</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>LB_COAG</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Coagulation Function</t>
   </si>
   <si>
     <t>LB_URIN</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>尿常规</t>
-  </si>
-  <si>
-    <t>LB_CHEM</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Chemistry</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Urinalysis</t>
+  </si>
+  <si>
+    <t>LB_UPRO</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>24- Hour Urinary Protein Quantity</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Pregnancy Test</t>
+  </si>
+  <si>
+    <t>THY</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Thyroid Function</t>
+  </si>
+  <si>
+    <t>VIRO</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Serum Virology</t>
+  </si>
+  <si>
+    <t>HBV</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>HBV-DNA test</t>
+  </si>
+  <si>
+    <t>HCV</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>HCV-RNA test</t>
+  </si>
+  <si>
+    <t>TSC</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Tumor Tissue Collection</t>
+  </si>
+  <si>
+    <t>IE</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Inclusion/Exclusion Criteria</t>
+  </si>
+  <si>
+    <t>ENROLL</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>SIM0609 administration</t>
+  </si>
+  <si>
+    <t>DLT</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>DLT Evaluation</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Biomarker Sample Collection</t>
+  </si>
+  <si>
+    <t>BIO100</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Biomarker Sample Collection (Unscheduled)</t>
+  </si>
+  <si>
+    <t>PSC</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>PD marker Sample Collection</t>
+  </si>
+  <si>
+    <t>PSC100</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>PD marker Sample Collection (Unscheduled)</t>
+  </si>
+  <si>
+    <t>PC1</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Pharmacokinetics sample collection (Single Timepoint)</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Pharmacokinetics sample collection (Multiple Timepoints)</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Pharmacokinetics sample collection (Multiple Timepoints for Part 2)</t>
+  </si>
+  <si>
+    <t>PC100</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Pharmacokinetics Sample Collection (Unscheduled)</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>ADA sample collection (Single Timepoint)</t>
+  </si>
+  <si>
+    <t>ADA100</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>ADA sample collection (Unscheduled)</t>
+  </si>
+  <si>
+    <t>TR_WEEK</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Oncology Response Assessment Week</t>
+  </si>
+  <si>
+    <t>TR_TL</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Target Lesion Results</t>
+  </si>
+  <si>
+    <t>TR_NTL</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Non-target Lesion Results</t>
+  </si>
+  <si>
+    <t>TR_NL</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>New Lesion Results</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Oncology Response Assessment (RECIST1.1)</t>
+  </si>
+  <si>
+    <t>CONT</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Visit Continuation</t>
+  </si>
+  <si>
+    <t>UA</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Unscheduled Assessment</t>
+  </si>
+  <si>
+    <t>LB1</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Other Lab Tests</t>
+  </si>
+  <si>
+    <t>CM_ANMYN</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Post Anti-Cancer Therapy-Medication summary</t>
+  </si>
+  <si>
+    <t>CM_ANM</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Post Anti-Cancer Therapy-Medication</t>
+  </si>
+  <si>
+    <t>CM_RAD</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Post Anti-Cancer Radiation Therapy</t>
+  </si>
+  <si>
+    <t>CM_ANT</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Post Anti-Cancer Surgery and Procedure</t>
+  </si>
+  <si>
+    <t>AEYN</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Adverse Events Summary</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Adverse Events</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Prior and Concomitant Medications(Non- tumor related)</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Prior and Concomitant Procedures (Non-tumor related)</t>
+  </si>
+  <si>
+    <t>DS_EOT</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>End of Treatment</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Death Report</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Survival Follow-up</t>
+  </si>
+  <si>
+    <t>DS_EOS</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>End of Study</t>
   </si>
 </sst>
 </file>
@@ -183,12 +753,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.632012367248535" customWidth="1"/>
+    <col min="1" max="1" width="12.813322067260742" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.98721694946289" customWidth="1"/>
+    <col min="3" max="3" width="64.92469787597656" customWidth="1"/>
     <col min="4" max="4" width="16.72708511352539" customWidth="1"/>
     <col min="5" max="5" width="9.679140090942383" customWidth="1"/>
     <col min="6" max="6" width="12.119486808776855" customWidth="1"/>
@@ -305,7 +875,7 @@
         <v>19</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>21</v>
@@ -316,7 +886,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>27</v>
@@ -337,7 +907,7 @@
         <v>19</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>21</v>
@@ -369,7 +939,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>21</v>
@@ -380,13 +950,13 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>18</v>
@@ -401,7 +971,7 @@
         <v>19</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L6" s="0" t="s">
         <v>21</v>
@@ -412,13 +982,13 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>18</v>
@@ -444,13 +1014,13 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>18</v>
@@ -465,12 +1035,2028 @@
         <v>19</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L8" s="0" t="s">
         <v>21</v>
       </c>
       <c r="M8" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L39" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L44" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L47" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L48" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L49" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L53" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L62" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L63" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L64" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L65" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L66" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K67" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L67" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L68" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K71" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="L71" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="0" t="s">
         <v>22</v>
       </c>
     </row>
